--- a/tools/chego_ne_hvataet.xlsx
+++ b/tools/chego_ne_hvataet.xlsx
@@ -629,7 +629,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>7 Доступная среда</t>
+          <t>7.1 Доступная среда</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2 Пожарная безопасность; 3 Градостроительство; 7 Доступная среда</t>
+          <t>2 Пожарная безопасность; 3 Градостроительство; 7.1 Доступная среда</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>9 Парковки</t>
+          <t>7.3 Парковки</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>8 Общественные здания</t>
+          <t>7.2 Общественные здания</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>8 Общественные здания; 9 Парковки</t>
+          <t>7.2 Общественные здания; 7.3 Парковки</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>9 Парковки</t>
+          <t>7.3 Парковки</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>9 Парковки</t>
+          <t>7.3 Парковки</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>9 Парковки</t>
+          <t>7.3 Парковки</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>8 Общественные здания</t>
+          <t>7.2 Общественные здания</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>7 Доступная среда</t>
+          <t>7.1 Доступная среда</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>7 Доступная среда; 2 Пожарная безопасность</t>
+          <t>7.1 Доступная среда; 2 Пожарная безопасность</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>7 Доступная среда</t>
+          <t>7.1 Доступная среда</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>7 Доступная среда</t>
+          <t>7.1 Доступная среда</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>7 Доступная среда</t>
+          <t>7.1 Доступная среда</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>2 Пожарная безопасность; 7 Доступная среда</t>
+          <t>2 Пожарная безопасность; 7.1 Доступная среда</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>7 Доступная среда</t>
+          <t>7.1 Доступная среда</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>7 Доступная среда</t>
+          <t>7.1 Доступная среда</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">

--- a/tools/chego_ne_hvataet.xlsx
+++ b/tools/chego_ne_hvataet.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Как читать" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Чего не хватает'!$A$1:$J$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Чего не хватает'!$A$1:$J$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2715,17 +2715,17 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Все разделы</t>
+          <t>7.4 Высотные жилые; 7.5 Высотные общественные; 2.16 Высотные здания</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Общее</t>
+          <t>Россия</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Раздел «Проектирование» и «Архитектура» — заготовки</t>
+          <t>СП 550.1311500.2026 (пожарная безопасность высотных зданий; заменяет СП 477.1325800.2020)</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -2735,24 +2735,380 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Содержимого нет.</t>
+          <t>Текст не загружен; СП 477 (ред. 02.08.2024) в портале используется, но может быть утрачивающим силу.</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Определить, что в них сравнивать.</t>
-        </is>
-      </c>
-      <c r="J48" s="9" t="inlineStr">
+          <t>Прислать PDF/текст СП 550; затем сверить разделы 2.16, 7.4, 7.5.</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>Высокий</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>7.4 Высотные жилые; 7.5 Высотные общественные</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>СП 267.1325800.2016 — официальная редакция (разделы 9, 10, 12 не вынесены)</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>Прочитан частично</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Прочитан по копии meganorm.ru (ред. 30.12.2020), не по «Техэксперт»; вынесен только раздел 6.</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>https://meganorm.ru/mega_doc/norm/metodika/0/sp_267_1325800_2016_svod_pravil_zdaniya_i_kompleksy_vysotnye.html</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Прислать PDF из «Техэксперт» для сверки.</t>
+        </is>
+      </c>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>7.5 Высотные общественные</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>СП 160.1325800.2014 (многофункциональные здания и комплексы)</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>Нет документа</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>На него отсылает СП 267 (п. 6.4, 6.19, 6.21); не читался.</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Прислать PDF.</t>
+        </is>
+      </c>
+      <c r="J50" s="7" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>7.6 Жилые здания до 75 м</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>СП 54.13330.2022 — полный текст (копия tiflocentre.ru неполная: нет разделов 5.3 и далее)</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>Прочитан частично</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Нет высоты помещений, кухонь, санузлов, лифтов, мусоропровода, приложений.</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>https://tiflocentre.ru/documents/sp_54.13330.2022.php</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Прислать PDF из «Техэксперт».</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>Высокий</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>7.4 Высотные жилые; 7.5 Высотные общественные; 7.6 Жилые до 75 м</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Сербия</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Правилники по высоким объектам и по стандартам жилья (архитектурная часть)</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>Нет документа</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Не найдены; для 7.4–7.6 стоит ⏳.</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>https://www.paragraf.rs</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Найти номера и тексты.</t>
+        </is>
+      </c>
+      <c r="J52" s="7" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>7.4 Высотные жилые; 7.5 Высотные общественные; 7.6 Жилые до 75 м</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Англия</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Approved Documents K, M Vol 1, B Vol 1 (жильё) и нормы для высотных зданий</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>Нет документа</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>AD M Vol 2 и AD B Vol 2 в портале есть; остальные тома для этих разделов не вынесены.</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/collections/approved-documents</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Скачать с gov.uk (доступен).</t>
+        </is>
+      </c>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>7.4 Высотные жилые; 7.5 Высотные общественные; 7.6 Жилые до 75 м</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>ЕС</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Германия — земельные нормы; Австрия OIB-RL 3/4; Испания CTE DB-SUA/HS; Франция — code de la construction</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>Нет документа</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Для 7.4–7.6 стоит ⏳.</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Найти и прислать.</t>
+        </is>
+      </c>
+      <c r="J54" s="7" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>7.4 Высотные жилые; 7.5 Высотные общественные; 7.6 Жилые до 75 м</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>ОАЭ</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Dubai Building Code (раздел для high-rise) и UAE Fire and Life Safety Code</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Нет доступа</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>FLSC не удалось получить; DBC используется только в других разделах.</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>https://dda.gov.ae/en/planning-development/codes-and-guidelines</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Прислать PDF.</t>
+        </is>
+      </c>
+      <c r="J55" s="7" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Все разделы</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Общее</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Раздел «Архитектура» (общий обзор): планировочные решения, общие требования — заготовка</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>Нет документа</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Общая часть не наполнена; подразделы 7.1–7.6 наполнены частично.</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Определить, что ещё сравнивать.</t>
+        </is>
+      </c>
+      <c r="J56" s="9" t="inlineStr">
         <is>
           <t>Низкий</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J48"/>
+  <autoFilter ref="A1:J56"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -2804,6 +3160,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId55"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2865,10 +3226,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
@@ -2887,19 +3248,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -2909,13 +3270,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
         <v>2</v>
@@ -2953,13 +3314,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -2997,13 +3358,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>4</v>

--- a/tools/chego_ne_hvataet.xlsx
+++ b/tools/chego_ne_hvataet.xlsx
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>7.4 Высотные жилые; 7.5 Высотные общественные; 2.16 Высотные здания</t>
+          <t>2.16 Высотные здания; 7.4; 7.5</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2725,29 +2725,29 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>СП 550.1311500.2026 (пожарная безопасность высотных зданий; заменяет СП 477.1325800.2020)</t>
-        </is>
-      </c>
-      <c r="E48" s="6" t="inlineStr">
-        <is>
-          <t>Нет документа</t>
+          <t>СП 550.1311500.2026 — официальная редакция «Техэксперт» и приказ МЧС об отмене СП 477</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>Прочитан частично</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Текст не загружен; СП 477 (ред. 02.08.2024) в портале используется, но может быть утрачивающим силу.</t>
+          <t>Прочитан по файлу пользователя («Гарант», 18.05.2026, пометка «не вступил в силу»; введён с 01.06.2026); в тексте нет указания, что СП 477 отменён. Разделы 7.1 (ПДВ), 7.2–7.4, 10 не вынесены.</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Прислать PDF/текст СП 550; затем сверить разделы 2.16, 7.4, 7.5.</t>
-        </is>
-      </c>
-      <c r="J48" s="5" t="inlineStr">
-        <is>
-          <t>Высокий</t>
+          <t>Подтвердить статус по приказу МЧС; прислать актуальную редакцию.</t>
+        </is>
+      </c>
+      <c r="J48" s="7" t="inlineStr">
+        <is>
+          <t>Средний</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>СП 54.13330.2022 — полный текст (копия tiflocentre.ru неполная: нет разделов 5.3 и далее)</t>
+          <t>СП 54.13330.2022 — вынесены не все разделы</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Нет высоты помещений, кухонь, санузлов, лифтов, мусоропровода, приложений.</t>
+          <t>Полный текст есть (файл «Гарант», 24.06.2026); в портал не вынесены санузлы, мусоропровод, пожарные требования (6.2), приложения.</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
@@ -2876,12 +2876,12 @@
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>Прислать PDF из «Техэксперт».</t>
-        </is>
-      </c>
-      <c r="J51" s="5" t="inlineStr">
-        <is>
-          <t>Высокий</t>
+          <t>Можно вынести без новых файлов.</t>
+        </is>
+      </c>
+      <c r="J51" s="9" t="inlineStr">
+        <is>
+          <t>Низкий</t>
         </is>
       </c>
     </row>
@@ -3254,13 +3254,13 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
